--- a/excel-data/restaurant.xlsx
+++ b/excel-data/restaurant.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyCreation\Web\mogumogu-pick\excel-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F635582-FE09-402A-8F30-D323CF9CD4CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC0030A1-C291-4125-AC00-F375C5E691D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4128" yWindow="2592" windowWidth="17280" windowHeight="9648" xr2:uid="{2C4057A3-4DF4-41B5-A441-0D94A14DFD1E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2C4057A3-4DF4-41B5-A441-0D94A14DFD1E}"/>
   </bookViews>
   <sheets>
     <sheet name="restaurant" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="196">
   <si>
     <t>restaurant_id</t>
   </si>
@@ -639,6 +639,14 @@
   </si>
   <si>
     <t>created_at</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否封存（軟刪除）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>is_archived</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1073,15 +1081,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E49155C-24E6-44A5-B674-54852AEBDB71}">
-  <dimension ref="A1:K45"/>
+  <dimension ref="A1:L45"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="4" width="22.77734375" style="1" customWidth="1"/>
-    <col min="5" max="7" width="22.77734375" customWidth="1"/>
-    <col min="8" max="11" width="22.77734375" style="1" customWidth="1"/>
+    <col min="1" max="5" width="22.77734375" style="1" customWidth="1"/>
+    <col min="6" max="9" width="22.77734375" customWidth="1"/>
+    <col min="10" max="12" width="22.77734375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>159</v>
       </c>
@@ -1095,28 +1103,31 @@
         <v>185</v>
       </c>
       <c r="E1" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="H1" s="3" t="s">
-        <v>188</v>
-      </c>
       <c r="I1" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="J1" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -1130,28 +1141,31 @@
         <v>186</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>1</v>
+        <v>187</v>
       </c>
       <c r="F2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>187</v>
-      </c>
       <c r="I2" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="J2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -1164,29 +1178,32 @@
       <c r="D3" s="1">
         <v>1</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="1">
+        <v>3</v>
+      </c>
+      <c r="F3" t="s">
         <v>163</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>165</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="1">
-        <v>3</v>
-      </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" s="4" t="s">
         <v>6</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>164</v>
       </c>
       <c r="K3" s="4" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L3" s="4" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -1199,29 +1216,32 @@
       <c r="D4" s="1">
         <v>2</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="1">
+        <v>1</v>
+      </c>
+      <c r="F4" t="s">
         <v>168</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>167</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="1">
-        <v>1</v>
-      </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" s="4" t="s">
         <v>9</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>166</v>
       </c>
       <c r="K4" s="4" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L4" s="4" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -1234,29 +1254,32 @@
       <c r="D5" s="1">
         <v>3</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="1">
+        <v>1</v>
+      </c>
+      <c r="F5" t="s">
         <v>10</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>13</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>11</v>
       </c>
-      <c r="H5" s="1">
-        <v>1</v>
-      </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" s="4" t="s">
         <v>12</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>7</v>
       </c>
       <c r="K5" s="4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L5" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -1269,29 +1292,32 @@
       <c r="D6" s="1">
         <v>4</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="1">
+        <v>1</v>
+      </c>
+      <c r="F6" t="s">
         <v>14</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>15</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
         <v>182</v>
       </c>
-      <c r="H6" s="1">
-        <v>1</v>
-      </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" s="4" t="s">
         <v>9</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>7</v>
       </c>
       <c r="K6" s="4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L6" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -1304,29 +1330,32 @@
       <c r="D7" s="1">
         <v>5</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="1">
+        <v>4</v>
+      </c>
+      <c r="F7" t="s">
         <v>170</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>171</v>
       </c>
-      <c r="G7" t="s">
+      <c r="H7" t="s">
         <v>16</v>
       </c>
-      <c r="H7" s="1">
-        <v>4</v>
-      </c>
-      <c r="I7" s="4" t="s">
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>172</v>
       </c>
       <c r="K7" s="4" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L7" s="4" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -1339,27 +1368,30 @@
       <c r="D8" s="1">
         <v>6</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="1">
+        <v>0</v>
+      </c>
+      <c r="F8" t="s">
         <v>173</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>174</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
         <v>18</v>
       </c>
-      <c r="H8" s="1">
-        <v>0</v>
-      </c>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4" t="s">
-        <v>175</v>
-      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" s="4"/>
       <c r="K8" s="4" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L8" s="4" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -1372,27 +1404,30 @@
       <c r="D9" s="1">
         <v>7</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="1">
+        <v>0</v>
+      </c>
+      <c r="F9" t="s">
         <v>19</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>22</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>20</v>
       </c>
-      <c r="H9" s="1">
-        <v>0</v>
-      </c>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4" t="s">
-        <v>21</v>
-      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" s="4"/>
       <c r="K9" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L9" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -1405,27 +1440,30 @@
       <c r="D10" s="1">
         <v>8</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="1">
+        <v>0</v>
+      </c>
+      <c r="F10" t="s">
         <v>23</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>177</v>
       </c>
-      <c r="G10" t="s">
+      <c r="H10" t="s">
         <v>24</v>
       </c>
-      <c r="H10" s="1">
-        <v>0</v>
-      </c>
-      <c r="I10" s="4"/>
-      <c r="J10" s="4" t="s">
-        <v>25</v>
-      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" s="4"/>
       <c r="K10" s="4" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L10" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -1438,29 +1476,32 @@
       <c r="D11" s="1">
         <v>9</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="1">
+        <v>3</v>
+      </c>
+      <c r="F11" t="s">
         <v>26</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>176</v>
       </c>
-      <c r="G11" t="s">
+      <c r="H11" t="s">
         <v>27</v>
       </c>
-      <c r="H11" s="1">
-        <v>3</v>
-      </c>
-      <c r="I11" s="4" t="s">
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="J11" s="4" t="s">
-        <v>29</v>
       </c>
       <c r="K11" s="4" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L11" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -1473,27 +1514,30 @@
       <c r="D12" s="1">
         <v>10</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E12" s="1">
+        <v>0</v>
+      </c>
+      <c r="F12" t="s">
         <v>30</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
         <v>33</v>
       </c>
-      <c r="G12" t="s">
+      <c r="H12" t="s">
         <v>31</v>
       </c>
-      <c r="H12" s="1">
-        <v>0</v>
-      </c>
-      <c r="I12" s="4"/>
-      <c r="J12" s="4" t="s">
-        <v>32</v>
-      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" s="4"/>
       <c r="K12" s="4" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L12" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -1506,27 +1550,30 @@
       <c r="D13" s="1">
         <v>11</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" s="1">
+        <v>0</v>
+      </c>
+      <c r="F13" t="s">
         <v>34</v>
       </c>
-      <c r="F13" t="s">
+      <c r="G13" t="s">
         <v>37</v>
       </c>
-      <c r="G13" t="s">
+      <c r="H13" t="s">
         <v>35</v>
       </c>
-      <c r="H13" s="1">
-        <v>0</v>
-      </c>
-      <c r="I13" s="4"/>
-      <c r="J13" s="4" t="s">
-        <v>36</v>
-      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" s="4"/>
       <c r="K13" s="4" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L13" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -1539,27 +1586,30 @@
       <c r="D14" s="1">
         <v>12</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E14" s="1">
+        <v>0</v>
+      </c>
+      <c r="F14" t="s">
         <v>38</v>
       </c>
-      <c r="F14" t="s">
+      <c r="G14" t="s">
         <v>41</v>
       </c>
-      <c r="G14" t="s">
+      <c r="H14" t="s">
         <v>39</v>
       </c>
-      <c r="H14" s="1">
-        <v>0</v>
-      </c>
-      <c r="I14" s="4"/>
-      <c r="J14" s="4" t="s">
-        <v>40</v>
-      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" s="4"/>
       <c r="K14" s="4" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L14" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -1572,29 +1622,32 @@
       <c r="D15" s="1">
         <v>13</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E15" s="1">
+        <v>1</v>
+      </c>
+      <c r="F15" t="s">
         <v>42</v>
       </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
         <v>46</v>
       </c>
-      <c r="G15" t="s">
+      <c r="H15" t="s">
         <v>43</v>
       </c>
-      <c r="H15" s="1">
-        <v>1</v>
-      </c>
-      <c r="I15" s="4" t="s">
+      <c r="I15" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" s="4" t="s">
         <v>44</v>
-      </c>
-      <c r="J15" s="4" t="s">
-        <v>45</v>
       </c>
       <c r="K15" s="4" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L15" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -1607,29 +1660,32 @@
       <c r="D16" s="1">
         <v>14</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E16" s="1">
+        <v>4</v>
+      </c>
+      <c r="F16" t="s">
         <v>47</v>
       </c>
-      <c r="F16" t="s">
+      <c r="G16" t="s">
         <v>51</v>
       </c>
-      <c r="G16" t="s">
+      <c r="H16" t="s">
         <v>48</v>
       </c>
-      <c r="H16" s="1">
-        <v>4</v>
-      </c>
-      <c r="I16" s="4" t="s">
+      <c r="I16" t="b">
+        <v>0</v>
+      </c>
+      <c r="J16" s="4" t="s">
         <v>49</v>
-      </c>
-      <c r="J16" s="4" t="s">
-        <v>50</v>
       </c>
       <c r="K16" s="4" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="17" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L16" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -1642,29 +1698,32 @@
       <c r="D17" s="1">
         <v>15</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E17" s="1">
+        <v>2</v>
+      </c>
+      <c r="F17" t="s">
         <v>52</v>
       </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
         <v>46</v>
       </c>
-      <c r="G17" t="s">
+      <c r="H17" t="s">
         <v>53</v>
       </c>
-      <c r="H17" s="1">
-        <v>2</v>
-      </c>
-      <c r="I17" s="4" t="s">
+      <c r="I17" t="b">
+        <v>0</v>
+      </c>
+      <c r="J17" s="4" t="s">
         <v>54</v>
-      </c>
-      <c r="J17" s="4" t="s">
-        <v>55</v>
       </c>
       <c r="K17" s="4" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="18" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L17" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -1677,29 +1736,32 @@
       <c r="D18" s="1">
         <v>16</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E18" s="1">
+        <v>1</v>
+      </c>
+      <c r="F18" t="s">
         <v>56</v>
       </c>
-      <c r="F18" t="s">
+      <c r="G18" t="s">
         <v>60</v>
       </c>
-      <c r="G18" t="s">
+      <c r="H18" t="s">
         <v>57</v>
       </c>
-      <c r="H18" s="1">
-        <v>1</v>
-      </c>
-      <c r="I18" s="4" t="s">
+      <c r="I18" t="b">
+        <v>0</v>
+      </c>
+      <c r="J18" s="4" t="s">
         <v>58</v>
-      </c>
-      <c r="J18" s="4" t="s">
-        <v>59</v>
       </c>
       <c r="K18" s="4" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="19" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L18" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -1712,29 +1774,32 @@
       <c r="D19" s="1">
         <v>17</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E19" s="1">
+        <v>3</v>
+      </c>
+      <c r="F19" t="s">
         <v>61</v>
       </c>
-      <c r="F19" t="s">
+      <c r="G19" t="s">
         <v>51</v>
       </c>
-      <c r="G19" t="s">
+      <c r="H19" t="s">
         <v>62</v>
       </c>
-      <c r="H19" s="1">
-        <v>3</v>
-      </c>
-      <c r="I19" s="4" t="s">
+      <c r="I19" t="b">
+        <v>0</v>
+      </c>
+      <c r="J19" s="4" t="s">
         <v>63</v>
-      </c>
-      <c r="J19" s="4" t="s">
-        <v>64</v>
       </c>
       <c r="K19" s="4" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="20" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L19" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -1747,26 +1812,29 @@
       <c r="D20" s="1">
         <v>18</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E20" s="1">
+        <v>5</v>
+      </c>
+      <c r="F20" t="s">
         <v>65</v>
       </c>
-      <c r="F20" t="s">
+      <c r="G20" t="s">
         <v>51</v>
       </c>
-      <c r="H20" s="1">
-        <v>5</v>
-      </c>
-      <c r="I20" s="4" t="s">
+      <c r="I20" t="b">
+        <v>0</v>
+      </c>
+      <c r="J20" s="4" t="s">
         <v>66</v>
-      </c>
-      <c r="J20" s="4" t="s">
-        <v>67</v>
       </c>
       <c r="K20" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="21" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L20" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -1779,26 +1847,29 @@
       <c r="D21" s="1">
         <v>19</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E21" s="1">
+        <v>2</v>
+      </c>
+      <c r="F21" t="s">
         <v>68</v>
       </c>
-      <c r="F21" t="s">
+      <c r="G21" t="s">
         <v>46</v>
       </c>
-      <c r="H21" s="1">
-        <v>2</v>
-      </c>
-      <c r="I21" s="4" t="s">
+      <c r="I21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J21" s="4" t="s">
         <v>69</v>
-      </c>
-      <c r="J21" s="4" t="s">
-        <v>70</v>
       </c>
       <c r="K21" s="4" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="22" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L21" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -1811,29 +1882,32 @@
       <c r="D22" s="1">
         <v>20</v>
       </c>
-      <c r="E22" t="s">
+      <c r="E22" s="1">
+        <v>2</v>
+      </c>
+      <c r="F22" t="s">
         <v>71</v>
       </c>
-      <c r="F22" t="s">
+      <c r="G22" t="s">
         <v>75</v>
       </c>
-      <c r="G22" t="s">
+      <c r="H22" t="s">
         <v>72</v>
       </c>
-      <c r="H22" s="1">
-        <v>2</v>
-      </c>
-      <c r="I22" s="4" t="s">
+      <c r="I22" t="b">
+        <v>0</v>
+      </c>
+      <c r="J22" s="4" t="s">
         <v>73</v>
-      </c>
-      <c r="J22" s="4" t="s">
-        <v>74</v>
       </c>
       <c r="K22" s="4" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="23" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L22" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -1846,20 +1920,20 @@
       <c r="D23" s="1">
         <v>21</v>
       </c>
-      <c r="E23" t="s">
+      <c r="E23" s="1">
+        <v>4</v>
+      </c>
+      <c r="F23" t="s">
         <v>76</v>
       </c>
-      <c r="F23" t="s">
+      <c r="G23" t="s">
         <v>79</v>
       </c>
-      <c r="G23" t="s">
+      <c r="H23" t="s">
         <v>77</v>
       </c>
-      <c r="H23" s="1">
-        <v>4</v>
-      </c>
-      <c r="I23" s="4" t="s">
-        <v>78</v>
+      <c r="I23" t="b">
+        <v>0</v>
       </c>
       <c r="J23" s="4" t="s">
         <v>78</v>
@@ -1867,8 +1941,11 @@
       <c r="K23" s="4" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="24" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L23" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -1881,27 +1958,30 @@
       <c r="D24" s="1">
         <v>22</v>
       </c>
-      <c r="E24" t="s">
+      <c r="E24" s="1">
+        <v>0</v>
+      </c>
+      <c r="F24" t="s">
         <v>80</v>
       </c>
-      <c r="F24" t="s">
+      <c r="G24" t="s">
         <v>83</v>
       </c>
-      <c r="G24" t="s">
+      <c r="H24" t="s">
         <v>81</v>
       </c>
-      <c r="H24" s="1">
-        <v>0</v>
-      </c>
-      <c r="I24" s="4"/>
-      <c r="J24" s="4" t="s">
-        <v>82</v>
-      </c>
+      <c r="I24" t="b">
+        <v>0</v>
+      </c>
+      <c r="J24" s="4"/>
       <c r="K24" s="4" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="25" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L24" s="4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>23</v>
       </c>
@@ -1914,24 +1994,27 @@
       <c r="D25" s="1">
         <v>23</v>
       </c>
-      <c r="E25" t="s">
+      <c r="E25" s="1">
+        <v>0</v>
+      </c>
+      <c r="F25" t="s">
         <v>84</v>
       </c>
-      <c r="F25" t="s">
+      <c r="G25" t="s">
         <v>79</v>
       </c>
-      <c r="H25" s="1">
-        <v>0</v>
-      </c>
-      <c r="I25" s="4"/>
-      <c r="J25" s="4" t="s">
-        <v>85</v>
-      </c>
+      <c r="I25" t="b">
+        <v>0</v>
+      </c>
+      <c r="J25" s="4"/>
       <c r="K25" s="4" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="26" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L25" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>24</v>
       </c>
@@ -1944,29 +2027,32 @@
       <c r="D26" s="1">
         <v>24</v>
       </c>
-      <c r="E26" t="s">
+      <c r="E26" s="1">
+        <v>2</v>
+      </c>
+      <c r="F26" t="s">
         <v>86</v>
       </c>
-      <c r="F26" t="s">
+      <c r="G26" t="s">
         <v>90</v>
       </c>
-      <c r="G26" t="s">
+      <c r="H26" t="s">
         <v>87</v>
       </c>
-      <c r="H26" s="1">
-        <v>2</v>
-      </c>
-      <c r="I26" s="4" t="s">
+      <c r="I26" t="b">
+        <v>0</v>
+      </c>
+      <c r="J26" s="4" t="s">
         <v>88</v>
-      </c>
-      <c r="J26" s="4" t="s">
-        <v>89</v>
       </c>
       <c r="K26" s="4" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="27" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L26" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>25</v>
       </c>
@@ -1979,26 +2065,29 @@
       <c r="D27" s="1">
         <v>25</v>
       </c>
-      <c r="E27" t="s">
+      <c r="E27" s="1">
+        <v>2</v>
+      </c>
+      <c r="F27" t="s">
         <v>91</v>
       </c>
-      <c r="F27" t="s">
+      <c r="G27" t="s">
         <v>94</v>
       </c>
-      <c r="H27" s="1">
-        <v>2</v>
-      </c>
-      <c r="I27" s="4" t="s">
+      <c r="I27" t="b">
+        <v>0</v>
+      </c>
+      <c r="J27" s="4" t="s">
         <v>92</v>
-      </c>
-      <c r="J27" s="4" t="s">
-        <v>93</v>
       </c>
       <c r="K27" s="4" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="28" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L27" s="4" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>26</v>
       </c>
@@ -2011,29 +2100,32 @@
       <c r="D28" s="1">
         <v>26</v>
       </c>
-      <c r="E28" t="s">
+      <c r="E28" s="1">
+        <v>1</v>
+      </c>
+      <c r="F28" t="s">
         <v>95</v>
       </c>
-      <c r="F28" t="s">
+      <c r="G28" t="s">
         <v>51</v>
       </c>
-      <c r="G28" t="s">
+      <c r="H28" t="s">
         <v>96</v>
       </c>
-      <c r="H28" s="1">
-        <v>1</v>
-      </c>
-      <c r="I28" s="4" t="s">
+      <c r="I28" t="b">
+        <v>0</v>
+      </c>
+      <c r="J28" s="4" t="s">
         <v>97</v>
-      </c>
-      <c r="J28" s="4" t="s">
-        <v>98</v>
       </c>
       <c r="K28" s="4" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="29" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L28" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>27</v>
       </c>
@@ -2046,29 +2138,32 @@
       <c r="D29" s="1">
         <v>27</v>
       </c>
-      <c r="E29" t="s">
+      <c r="E29" s="1">
+        <v>4</v>
+      </c>
+      <c r="F29" t="s">
         <v>99</v>
       </c>
-      <c r="F29" t="s">
+      <c r="G29" t="s">
         <v>75</v>
       </c>
-      <c r="G29" t="s">
+      <c r="H29" t="s">
         <v>100</v>
       </c>
-      <c r="H29" s="1">
-        <v>4</v>
-      </c>
-      <c r="I29" s="4" t="s">
+      <c r="I29" t="b">
+        <v>0</v>
+      </c>
+      <c r="J29" s="4" t="s">
         <v>101</v>
-      </c>
-      <c r="J29" s="4" t="s">
-        <v>102</v>
       </c>
       <c r="K29" s="4" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="30" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L29" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>28</v>
       </c>
@@ -2081,29 +2176,32 @@
       <c r="D30" s="1">
         <v>28</v>
       </c>
-      <c r="E30" t="s">
+      <c r="E30" s="1">
+        <v>3</v>
+      </c>
+      <c r="F30" t="s">
         <v>103</v>
       </c>
-      <c r="F30" t="s">
+      <c r="G30" t="s">
         <v>83</v>
       </c>
-      <c r="G30" t="s">
+      <c r="H30" t="s">
         <v>104</v>
       </c>
-      <c r="H30" s="1">
-        <v>3</v>
-      </c>
-      <c r="I30" s="4" t="s">
+      <c r="I30" t="b">
+        <v>0</v>
+      </c>
+      <c r="J30" s="4" t="s">
         <v>105</v>
-      </c>
-      <c r="J30" s="4" t="s">
-        <v>106</v>
       </c>
       <c r="K30" s="4" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="31" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L30" s="4" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>29</v>
       </c>
@@ -2116,26 +2214,29 @@
       <c r="D31" s="1">
         <v>29</v>
       </c>
-      <c r="E31" t="s">
+      <c r="E31" s="1">
+        <v>5</v>
+      </c>
+      <c r="F31" t="s">
         <v>107</v>
       </c>
-      <c r="F31" t="s">
+      <c r="G31" t="s">
         <v>51</v>
       </c>
-      <c r="H31" s="1">
-        <v>5</v>
-      </c>
-      <c r="I31" s="4" t="s">
+      <c r="I31" t="b">
+        <v>0</v>
+      </c>
+      <c r="J31" s="4" t="s">
         <v>108</v>
-      </c>
-      <c r="J31" s="4" t="s">
-        <v>109</v>
       </c>
       <c r="K31" s="4" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="32" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L31" s="4" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>30</v>
       </c>
@@ -2148,26 +2249,29 @@
       <c r="D32" s="1">
         <v>30</v>
       </c>
-      <c r="E32" t="s">
+      <c r="E32" s="1">
+        <v>1</v>
+      </c>
+      <c r="F32" t="s">
         <v>110</v>
       </c>
-      <c r="F32" t="s">
+      <c r="G32" t="s">
         <v>113</v>
       </c>
-      <c r="H32" s="1">
-        <v>1</v>
-      </c>
-      <c r="I32" s="4" t="s">
+      <c r="I32" t="b">
+        <v>0</v>
+      </c>
+      <c r="J32" s="4" t="s">
         <v>111</v>
-      </c>
-      <c r="J32" s="4" t="s">
-        <v>112</v>
       </c>
       <c r="K32" s="4" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="33" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L32" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>31</v>
       </c>
@@ -2180,20 +2284,20 @@
       <c r="D33" s="1">
         <v>31</v>
       </c>
-      <c r="E33" t="s">
+      <c r="E33" s="1">
+        <v>2</v>
+      </c>
+      <c r="F33" t="s">
         <v>114</v>
       </c>
-      <c r="F33" t="s">
+      <c r="G33" t="s">
         <v>117</v>
       </c>
-      <c r="G33" t="s">
+      <c r="H33" t="s">
         <v>115</v>
       </c>
-      <c r="H33" s="1">
-        <v>2</v>
-      </c>
-      <c r="I33" s="4" t="s">
-        <v>116</v>
+      <c r="I33" t="b">
+        <v>0</v>
       </c>
       <c r="J33" s="4" t="s">
         <v>116</v>
@@ -2201,8 +2305,11 @@
       <c r="K33" s="4" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="34" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L33" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>32</v>
       </c>
@@ -2215,20 +2322,20 @@
       <c r="D34" s="1">
         <v>32</v>
       </c>
-      <c r="E34" t="s">
+      <c r="E34" s="1">
+        <v>1</v>
+      </c>
+      <c r="F34" t="s">
         <v>118</v>
       </c>
-      <c r="F34" t="s">
+      <c r="G34" t="s">
         <v>83</v>
       </c>
-      <c r="G34" t="s">
+      <c r="H34" t="s">
         <v>119</v>
       </c>
-      <c r="H34" s="1">
-        <v>1</v>
-      </c>
-      <c r="I34" s="4" t="s">
-        <v>120</v>
+      <c r="I34" t="b">
+        <v>0</v>
       </c>
       <c r="J34" s="4" t="s">
         <v>120</v>
@@ -2236,8 +2343,11 @@
       <c r="K34" s="4" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="35" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L34" s="4" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>33</v>
       </c>
@@ -2250,29 +2360,32 @@
       <c r="D35" s="1">
         <v>33</v>
       </c>
-      <c r="E35" t="s">
+      <c r="E35" s="1">
+        <v>1</v>
+      </c>
+      <c r="F35" t="s">
         <v>178</v>
       </c>
-      <c r="F35" t="s">
+      <c r="G35" t="s">
         <v>179</v>
       </c>
-      <c r="G35" t="s">
+      <c r="H35" t="s">
         <v>121</v>
       </c>
-      <c r="H35" s="1">
-        <v>1</v>
-      </c>
-      <c r="I35" s="4" t="s">
+      <c r="I35" t="b">
+        <v>0</v>
+      </c>
+      <c r="J35" s="4" t="s">
         <v>122</v>
-      </c>
-      <c r="J35" s="4" t="s">
-        <v>123</v>
       </c>
       <c r="K35" s="4" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="36" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L35" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>34</v>
       </c>
@@ -2285,24 +2398,27 @@
       <c r="D36" s="1">
         <v>34</v>
       </c>
-      <c r="E36" t="s">
+      <c r="E36" s="1">
+        <v>0</v>
+      </c>
+      <c r="F36" t="s">
         <v>124</v>
       </c>
-      <c r="F36" t="s">
+      <c r="G36" t="s">
         <v>60</v>
       </c>
-      <c r="H36" s="1">
-        <v>0</v>
-      </c>
-      <c r="I36" s="4"/>
-      <c r="J36" s="4" t="s">
-        <v>125</v>
-      </c>
+      <c r="I36" t="b">
+        <v>0</v>
+      </c>
+      <c r="J36" s="4"/>
       <c r="K36" s="4" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="37" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L36" s="4" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>35</v>
       </c>
@@ -2315,27 +2431,30 @@
       <c r="D37" s="1">
         <v>35</v>
       </c>
-      <c r="E37" t="s">
+      <c r="E37" s="1">
+        <v>0</v>
+      </c>
+      <c r="F37" t="s">
         <v>126</v>
       </c>
-      <c r="F37" t="s">
+      <c r="G37" t="s">
         <v>60</v>
       </c>
-      <c r="G37" t="s">
+      <c r="H37" t="s">
         <v>127</v>
       </c>
-      <c r="H37" s="1">
-        <v>0</v>
-      </c>
-      <c r="I37" s="4"/>
-      <c r="J37" s="4" t="s">
-        <v>128</v>
-      </c>
+      <c r="I37" t="b">
+        <v>0</v>
+      </c>
+      <c r="J37" s="4"/>
       <c r="K37" s="4" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="38" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L37" s="4" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>36</v>
       </c>
@@ -2348,26 +2467,29 @@
       <c r="D38" s="1">
         <v>36</v>
       </c>
-      <c r="E38" t="s">
+      <c r="E38" s="1">
+        <v>1</v>
+      </c>
+      <c r="F38" t="s">
         <v>129</v>
       </c>
-      <c r="F38" t="s">
+      <c r="G38" t="s">
         <v>79</v>
       </c>
-      <c r="H38" s="1">
-        <v>1</v>
-      </c>
-      <c r="I38" s="4" t="s">
+      <c r="I38" t="b">
+        <v>0</v>
+      </c>
+      <c r="J38" s="4" t="s">
         <v>130</v>
-      </c>
-      <c r="J38" s="4" t="s">
-        <v>131</v>
       </c>
       <c r="K38" s="4" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="39" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L38" s="4" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>37</v>
       </c>
@@ -2380,29 +2502,32 @@
       <c r="D39" s="1">
         <v>37</v>
       </c>
-      <c r="E39" t="s">
+      <c r="E39" s="1">
+        <v>2</v>
+      </c>
+      <c r="F39" t="s">
         <v>132</v>
       </c>
-      <c r="F39" t="s">
+      <c r="G39" t="s">
         <v>136</v>
       </c>
-      <c r="G39" t="s">
+      <c r="H39" t="s">
         <v>133</v>
       </c>
-      <c r="H39" s="1">
-        <v>2</v>
-      </c>
-      <c r="I39" s="4" t="s">
+      <c r="I39" t="b">
+        <v>0</v>
+      </c>
+      <c r="J39" s="4" t="s">
         <v>134</v>
-      </c>
-      <c r="J39" s="4" t="s">
-        <v>135</v>
       </c>
       <c r="K39" s="4" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="40" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L39" s="4" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>38</v>
       </c>
@@ -2415,27 +2540,30 @@
       <c r="D40" s="1">
         <v>38</v>
       </c>
-      <c r="E40" t="s">
+      <c r="E40" s="1">
+        <v>0</v>
+      </c>
+      <c r="F40" t="s">
         <v>137</v>
       </c>
-      <c r="F40" t="s">
+      <c r="G40" t="s">
         <v>140</v>
       </c>
-      <c r="G40" t="s">
+      <c r="H40" t="s">
         <v>138</v>
       </c>
-      <c r="H40" s="1">
-        <v>0</v>
-      </c>
-      <c r="I40" s="4"/>
-      <c r="J40" s="4" t="s">
-        <v>139</v>
-      </c>
+      <c r="I40" t="b">
+        <v>0</v>
+      </c>
+      <c r="J40" s="4"/>
       <c r="K40" s="4" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="41" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L40" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>39</v>
       </c>
@@ -2448,29 +2576,32 @@
       <c r="D41" s="1">
         <v>39</v>
       </c>
-      <c r="E41" t="s">
+      <c r="E41" s="1">
+        <v>1</v>
+      </c>
+      <c r="F41" t="s">
         <v>141</v>
       </c>
-      <c r="F41" t="s">
+      <c r="G41" t="s">
         <v>83</v>
       </c>
-      <c r="G41" t="s">
+      <c r="H41" t="s">
         <v>142</v>
       </c>
-      <c r="H41" s="1">
-        <v>1</v>
-      </c>
-      <c r="I41" s="4" t="s">
+      <c r="I41" t="b">
+        <v>0</v>
+      </c>
+      <c r="J41" s="4" t="s">
         <v>143</v>
-      </c>
-      <c r="J41" s="4" t="s">
-        <v>144</v>
       </c>
       <c r="K41" s="4" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="42" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L41" s="4" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>40</v>
       </c>
@@ -2483,27 +2614,30 @@
       <c r="D42" s="1">
         <v>40</v>
       </c>
-      <c r="E42" t="s">
+      <c r="E42" s="1">
+        <v>0</v>
+      </c>
+      <c r="F42" t="s">
         <v>145</v>
       </c>
-      <c r="F42" t="s">
+      <c r="G42" t="s">
         <v>169</v>
       </c>
-      <c r="G42" t="s">
+      <c r="H42" t="s">
         <v>146</v>
       </c>
-      <c r="H42" s="1">
-        <v>0</v>
-      </c>
-      <c r="I42" s="4"/>
-      <c r="J42" s="4" t="s">
-        <v>147</v>
-      </c>
+      <c r="I42" t="b">
+        <v>0</v>
+      </c>
+      <c r="J42" s="4"/>
       <c r="K42" s="4" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="43" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L42" s="4" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>41</v>
       </c>
@@ -2516,29 +2650,32 @@
       <c r="D43" s="1">
         <v>41</v>
       </c>
-      <c r="E43" t="s">
+      <c r="E43" s="1">
+        <v>3</v>
+      </c>
+      <c r="F43" t="s">
         <v>148</v>
       </c>
-      <c r="F43" t="s">
+      <c r="G43" t="s">
         <v>75</v>
       </c>
-      <c r="G43" t="s">
+      <c r="H43" t="s">
         <v>149</v>
       </c>
-      <c r="H43" s="1">
-        <v>3</v>
-      </c>
-      <c r="I43" s="4" t="s">
+      <c r="I43" t="b">
+        <v>0</v>
+      </c>
+      <c r="J43" s="4" t="s">
         <v>150</v>
-      </c>
-      <c r="J43" s="4" t="s">
-        <v>151</v>
       </c>
       <c r="K43" s="4" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="44" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L43" s="4" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>42</v>
       </c>
@@ -2551,29 +2688,32 @@
       <c r="D44" s="1">
         <v>42</v>
       </c>
-      <c r="E44" t="s">
+      <c r="E44" s="1">
+        <v>1</v>
+      </c>
+      <c r="F44" t="s">
         <v>152</v>
       </c>
-      <c r="F44" t="s">
+      <c r="G44" t="s">
         <v>94</v>
       </c>
-      <c r="G44" t="s">
+      <c r="H44" t="s">
         <v>153</v>
       </c>
-      <c r="H44" s="1">
-        <v>1</v>
-      </c>
-      <c r="I44" s="4" t="s">
+      <c r="I44" t="b">
+        <v>0</v>
+      </c>
+      <c r="J44" s="4" t="s">
         <v>154</v>
-      </c>
-      <c r="J44" s="4" t="s">
-        <v>155</v>
       </c>
       <c r="K44" s="4" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="45" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L44" s="4" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>43</v>
       </c>
@@ -2586,25 +2726,28 @@
       <c r="D45" s="1">
         <v>43</v>
       </c>
-      <c r="E45" t="s">
+      <c r="E45" s="1">
+        <v>4</v>
+      </c>
+      <c r="F45" t="s">
         <v>156</v>
       </c>
-      <c r="F45" t="s">
+      <c r="G45" t="s">
         <v>79</v>
       </c>
-      <c r="G45" t="s">
+      <c r="H45" t="s">
         <v>157</v>
       </c>
-      <c r="H45" s="1">
-        <v>4</v>
-      </c>
-      <c r="I45" s="4" t="s">
-        <v>158</v>
+      <c r="I45" t="b">
+        <v>0</v>
       </c>
       <c r="J45" s="4" t="s">
         <v>158</v>
       </c>
       <c r="K45" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="L45" s="4" t="s">
         <v>158</v>
       </c>
     </row>

--- a/excel-data/restaurant.xlsx
+++ b/excel-data/restaurant.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyCreation\Web\mogumogu-pick\excel-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC0030A1-C291-4125-AC00-F375C5E691D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCBCBB03-6D46-4202-8945-50FA3121ECAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2C4057A3-4DF4-41B5-A441-0D94A14DFD1E}"/>
+    <workbookView xWindow="1164" yWindow="2592" windowWidth="17280" windowHeight="9648" xr2:uid="{2C4057A3-4DF4-41B5-A441-0D94A14DFD1E}"/>
   </bookViews>
   <sheets>
     <sheet name="restaurant" sheetId="1" r:id="rId1"/>
@@ -606,14 +606,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>群組內排序</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>display_order</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>selected_count</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -647,6 +639,14 @@
   </si>
   <si>
     <t>is_archived</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>display_order_id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>群組內排序 ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1100,10 +1100,10 @@
         <v>183</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>160</v>
@@ -1115,16 +1115,16 @@
         <v>161</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="J1" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="K1" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="K1" s="3" t="s">
-        <v>191</v>
-      </c>
       <c r="L1" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
@@ -1138,10 +1138,10 @@
         <v>184</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>1</v>
@@ -1153,16 +1153,16 @@
         <v>2</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">

--- a/excel-data/restaurant.xlsx
+++ b/excel-data/restaurant.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyCreation\Web\mogumogu-pick\excel-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCBCBB03-6D46-4202-8945-50FA3121ECAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6789BA7-6CD3-4AE0-9250-6E55426C6123}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1164" yWindow="2592" windowWidth="17280" windowHeight="9648" xr2:uid="{2C4057A3-4DF4-41B5-A441-0D94A14DFD1E}"/>
+    <workbookView xWindow="2256" yWindow="2592" windowWidth="17280" windowHeight="9648" xr2:uid="{2C4057A3-4DF4-41B5-A441-0D94A14DFD1E}"/>
   </bookViews>
   <sheets>
     <sheet name="restaurant" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="194">
   <si>
     <t>restaurant_id</t>
   </si>
@@ -631,14 +631,6 @@
   </si>
   <si>
     <t>created_at</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>是否封存（軟刪除）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>is_archived</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1081,15 +1073,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E49155C-24E6-44A5-B674-54852AEBDB71}">
-  <dimension ref="A1:L45"/>
+  <dimension ref="A1:K45"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="5" width="22.77734375" style="1" customWidth="1"/>
-    <col min="6" max="9" width="22.77734375" customWidth="1"/>
-    <col min="10" max="12" width="22.77734375" style="1" customWidth="1"/>
+    <col min="6" max="8" width="22.77734375" customWidth="1"/>
+    <col min="9" max="11" width="22.77734375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>159</v>
       </c>
@@ -1100,7 +1092,7 @@
         <v>183</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>186</v>
@@ -1115,19 +1107,16 @@
         <v>161</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="L1" s="3" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -1138,7 +1127,7 @@
         <v>184</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>185</v>
@@ -1153,19 +1142,16 @@
         <v>2</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>193</v>
+        <v>3</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>3</v>
+        <v>191</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="L2" s="2" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -1190,20 +1176,17 @@
       <c r="H3" t="s">
         <v>5</v>
       </c>
-      <c r="I3" t="b">
-        <v>0</v>
+      <c r="I3" s="4" t="s">
+        <v>6</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>6</v>
+        <v>164</v>
       </c>
       <c r="K3" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="L3" s="4" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -1228,20 +1211,17 @@
       <c r="H4" t="s">
         <v>8</v>
       </c>
-      <c r="I4" t="b">
-        <v>0</v>
+      <c r="I4" s="4" t="s">
+        <v>9</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>9</v>
+        <v>166</v>
       </c>
       <c r="K4" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="L4" s="4" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -1266,20 +1246,17 @@
       <c r="H5" t="s">
         <v>11</v>
       </c>
-      <c r="I5" t="b">
-        <v>0</v>
+      <c r="I5" s="4" t="s">
+        <v>12</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="K5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="L5" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -1304,20 +1281,17 @@
       <c r="H6" t="s">
         <v>182</v>
       </c>
-      <c r="I6" t="b">
-        <v>0</v>
+      <c r="I6" s="4" t="s">
+        <v>9</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K6" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="L6" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>5</v>
       </c>
@@ -1342,20 +1316,17 @@
       <c r="H7" t="s">
         <v>16</v>
       </c>
-      <c r="I7" t="b">
-        <v>0</v>
+      <c r="I7" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>17</v>
+        <v>172</v>
       </c>
       <c r="K7" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="L7" s="4" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -1380,18 +1351,15 @@
       <c r="H8" t="s">
         <v>18</v>
       </c>
-      <c r="I8" t="b">
-        <v>0</v>
-      </c>
-      <c r="J8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4" t="s">
+        <v>175</v>
+      </c>
       <c r="K8" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="L8" s="4" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -1416,18 +1384,15 @@
       <c r="H9" t="s">
         <v>20</v>
       </c>
-      <c r="I9" t="b">
-        <v>0</v>
-      </c>
-      <c r="J9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4" t="s">
+        <v>21</v>
+      </c>
       <c r="K9" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="L9" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -1452,18 +1417,15 @@
       <c r="H10" t="s">
         <v>24</v>
       </c>
-      <c r="I10" t="b">
-        <v>0</v>
-      </c>
-      <c r="J10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4" t="s">
+        <v>25</v>
+      </c>
       <c r="K10" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="L10" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>9</v>
       </c>
@@ -1488,20 +1450,17 @@
       <c r="H11" t="s">
         <v>27</v>
       </c>
-      <c r="I11" t="b">
-        <v>0</v>
+      <c r="I11" s="4" t="s">
+        <v>28</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K11" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="L11" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -1526,18 +1485,15 @@
       <c r="H12" t="s">
         <v>31</v>
       </c>
-      <c r="I12" t="b">
-        <v>0</v>
-      </c>
-      <c r="J12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4" t="s">
+        <v>32</v>
+      </c>
       <c r="K12" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="L12" s="4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -1562,18 +1518,15 @@
       <c r="H13" t="s">
         <v>35</v>
       </c>
-      <c r="I13" t="b">
-        <v>0</v>
-      </c>
-      <c r="J13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4" t="s">
+        <v>36</v>
+      </c>
       <c r="K13" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="L13" s="4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -1598,18 +1551,15 @@
       <c r="H14" t="s">
         <v>39</v>
       </c>
-      <c r="I14" t="b">
-        <v>0</v>
-      </c>
-      <c r="J14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4" t="s">
+        <v>40</v>
+      </c>
       <c r="K14" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="L14" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -1634,20 +1584,17 @@
       <c r="H15" t="s">
         <v>43</v>
       </c>
-      <c r="I15" t="b">
-        <v>0</v>
+      <c r="I15" s="4" t="s">
+        <v>44</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K15" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="L15" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -1672,20 +1619,17 @@
       <c r="H16" t="s">
         <v>48</v>
       </c>
-      <c r="I16" t="b">
-        <v>0</v>
+      <c r="I16" s="4" t="s">
+        <v>49</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K16" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="L16" s="4" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -1710,20 +1654,17 @@
       <c r="H17" t="s">
         <v>53</v>
       </c>
-      <c r="I17" t="b">
-        <v>0</v>
+      <c r="I17" s="4" t="s">
+        <v>54</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K17" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="L17" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -1748,20 +1689,17 @@
       <c r="H18" t="s">
         <v>57</v>
       </c>
-      <c r="I18" t="b">
-        <v>0</v>
+      <c r="I18" s="4" t="s">
+        <v>58</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K18" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="L18" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -1786,20 +1724,17 @@
       <c r="H19" t="s">
         <v>62</v>
       </c>
-      <c r="I19" t="b">
-        <v>0</v>
+      <c r="I19" s="4" t="s">
+        <v>63</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K19" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="L19" s="4" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -1821,20 +1756,17 @@
       <c r="G20" t="s">
         <v>51</v>
       </c>
-      <c r="I20" t="b">
-        <v>0</v>
+      <c r="I20" s="4" t="s">
+        <v>66</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K20" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="L20" s="4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -1856,20 +1788,17 @@
       <c r="G21" t="s">
         <v>46</v>
       </c>
-      <c r="I21" t="b">
-        <v>0</v>
+      <c r="I21" s="4" t="s">
+        <v>69</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K21" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="L21" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -1894,20 +1823,17 @@
       <c r="H22" t="s">
         <v>72</v>
       </c>
-      <c r="I22" t="b">
-        <v>0</v>
+      <c r="I22" s="4" t="s">
+        <v>73</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K22" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="L22" s="4" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -1932,8 +1858,8 @@
       <c r="H23" t="s">
         <v>77</v>
       </c>
-      <c r="I23" t="b">
-        <v>0</v>
+      <c r="I23" s="4" t="s">
+        <v>78</v>
       </c>
       <c r="J23" s="4" t="s">
         <v>78</v>
@@ -1941,11 +1867,8 @@
       <c r="K23" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="L23" s="4" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="24" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -1970,18 +1893,15 @@
       <c r="H24" t="s">
         <v>81</v>
       </c>
-      <c r="I24" t="b">
-        <v>0</v>
-      </c>
-      <c r="J24" s="4"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="4" t="s">
+        <v>82</v>
+      </c>
       <c r="K24" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="L24" s="4" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>23</v>
       </c>
@@ -2003,18 +1923,15 @@
       <c r="G25" t="s">
         <v>79</v>
       </c>
-      <c r="I25" t="b">
-        <v>0</v>
-      </c>
-      <c r="J25" s="4"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4" t="s">
+        <v>85</v>
+      </c>
       <c r="K25" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="L25" s="4" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>24</v>
       </c>
@@ -2039,20 +1956,17 @@
       <c r="H26" t="s">
         <v>87</v>
       </c>
-      <c r="I26" t="b">
-        <v>0</v>
+      <c r="I26" s="4" t="s">
+        <v>88</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K26" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="L26" s="4" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="27" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>25</v>
       </c>
@@ -2074,20 +1988,17 @@
       <c r="G27" t="s">
         <v>94</v>
       </c>
-      <c r="I27" t="b">
-        <v>0</v>
+      <c r="I27" s="4" t="s">
+        <v>92</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K27" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="L27" s="4" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="28" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>26</v>
       </c>
@@ -2112,20 +2023,17 @@
       <c r="H28" t="s">
         <v>96</v>
       </c>
-      <c r="I28" t="b">
-        <v>0</v>
+      <c r="I28" s="4" t="s">
+        <v>97</v>
       </c>
       <c r="J28" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K28" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="L28" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="29" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>27</v>
       </c>
@@ -2150,20 +2058,17 @@
       <c r="H29" t="s">
         <v>100</v>
       </c>
-      <c r="I29" t="b">
-        <v>0</v>
+      <c r="I29" s="4" t="s">
+        <v>101</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K29" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="L29" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="30" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>28</v>
       </c>
@@ -2188,20 +2093,17 @@
       <c r="H30" t="s">
         <v>104</v>
       </c>
-      <c r="I30" t="b">
-        <v>0</v>
+      <c r="I30" s="4" t="s">
+        <v>105</v>
       </c>
       <c r="J30" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K30" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="L30" s="4" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="31" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>29</v>
       </c>
@@ -2223,20 +2125,17 @@
       <c r="G31" t="s">
         <v>51</v>
       </c>
-      <c r="I31" t="b">
-        <v>0</v>
+      <c r="I31" s="4" t="s">
+        <v>108</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K31" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="L31" s="4" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="32" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>30</v>
       </c>
@@ -2258,20 +2157,17 @@
       <c r="G32" t="s">
         <v>113</v>
       </c>
-      <c r="I32" t="b">
-        <v>0</v>
+      <c r="I32" s="4" t="s">
+        <v>111</v>
       </c>
       <c r="J32" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K32" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="L32" s="4" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="33" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>31</v>
       </c>
@@ -2296,8 +2192,8 @@
       <c r="H33" t="s">
         <v>115</v>
       </c>
-      <c r="I33" t="b">
-        <v>0</v>
+      <c r="I33" s="4" t="s">
+        <v>116</v>
       </c>
       <c r="J33" s="4" t="s">
         <v>116</v>
@@ -2305,11 +2201,8 @@
       <c r="K33" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="L33" s="4" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="34" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>32</v>
       </c>
@@ -2334,8 +2227,8 @@
       <c r="H34" t="s">
         <v>119</v>
       </c>
-      <c r="I34" t="b">
-        <v>0</v>
+      <c r="I34" s="4" t="s">
+        <v>120</v>
       </c>
       <c r="J34" s="4" t="s">
         <v>120</v>
@@ -2343,11 +2236,8 @@
       <c r="K34" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="L34" s="4" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="35" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>33</v>
       </c>
@@ -2372,20 +2262,17 @@
       <c r="H35" t="s">
         <v>121</v>
       </c>
-      <c r="I35" t="b">
-        <v>0</v>
+      <c r="I35" s="4" t="s">
+        <v>122</v>
       </c>
       <c r="J35" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="K35" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="L35" s="4" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="36" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>34</v>
       </c>
@@ -2407,18 +2294,15 @@
       <c r="G36" t="s">
         <v>60</v>
       </c>
-      <c r="I36" t="b">
-        <v>0</v>
-      </c>
-      <c r="J36" s="4"/>
+      <c r="I36" s="4"/>
+      <c r="J36" s="4" t="s">
+        <v>125</v>
+      </c>
       <c r="K36" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="L36" s="4" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="37" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>35</v>
       </c>
@@ -2443,18 +2327,15 @@
       <c r="H37" t="s">
         <v>127</v>
       </c>
-      <c r="I37" t="b">
-        <v>0</v>
-      </c>
-      <c r="J37" s="4"/>
+      <c r="I37" s="4"/>
+      <c r="J37" s="4" t="s">
+        <v>128</v>
+      </c>
       <c r="K37" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="L37" s="4" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="38" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>36</v>
       </c>
@@ -2476,20 +2357,17 @@
       <c r="G38" t="s">
         <v>79</v>
       </c>
-      <c r="I38" t="b">
-        <v>0</v>
+      <c r="I38" s="4" t="s">
+        <v>130</v>
       </c>
       <c r="J38" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K38" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="L38" s="4" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="39" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>37</v>
       </c>
@@ -2514,20 +2392,17 @@
       <c r="H39" t="s">
         <v>133</v>
       </c>
-      <c r="I39" t="b">
-        <v>0</v>
+      <c r="I39" s="4" t="s">
+        <v>134</v>
       </c>
       <c r="J39" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K39" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="L39" s="4" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="40" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>38</v>
       </c>
@@ -2552,18 +2427,15 @@
       <c r="H40" t="s">
         <v>138</v>
       </c>
-      <c r="I40" t="b">
-        <v>0</v>
-      </c>
-      <c r="J40" s="4"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4" t="s">
+        <v>139</v>
+      </c>
       <c r="K40" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="L40" s="4" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="41" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>39</v>
       </c>
@@ -2588,20 +2460,17 @@
       <c r="H41" t="s">
         <v>142</v>
       </c>
-      <c r="I41" t="b">
-        <v>0</v>
+      <c r="I41" s="4" t="s">
+        <v>143</v>
       </c>
       <c r="J41" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K41" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="L41" s="4" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="42" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>40</v>
       </c>
@@ -2626,18 +2495,15 @@
       <c r="H42" t="s">
         <v>146</v>
       </c>
-      <c r="I42" t="b">
-        <v>0</v>
-      </c>
-      <c r="J42" s="4"/>
+      <c r="I42" s="4"/>
+      <c r="J42" s="4" t="s">
+        <v>147</v>
+      </c>
       <c r="K42" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="L42" s="4" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="43" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>41</v>
       </c>
@@ -2662,20 +2528,17 @@
       <c r="H43" t="s">
         <v>149</v>
       </c>
-      <c r="I43" t="b">
-        <v>0</v>
+      <c r="I43" s="4" t="s">
+        <v>150</v>
       </c>
       <c r="J43" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="K43" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="L43" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="44" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>42</v>
       </c>
@@ -2700,20 +2563,17 @@
       <c r="H44" t="s">
         <v>153</v>
       </c>
-      <c r="I44" t="b">
-        <v>0</v>
+      <c r="I44" s="4" t="s">
+        <v>154</v>
       </c>
       <c r="J44" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K44" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="L44" s="4" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="45" spans="1:11" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>43</v>
       </c>
@@ -2738,16 +2598,13 @@
       <c r="H45" t="s">
         <v>157</v>
       </c>
-      <c r="I45" t="b">
-        <v>0</v>
+      <c r="I45" s="4" t="s">
+        <v>158</v>
       </c>
       <c r="J45" s="4" t="s">
         <v>158</v>
       </c>
       <c r="K45" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="L45" s="4" t="s">
         <v>158</v>
       </c>
     </row>
